--- a/data_folder/bev_electronics_wiring/input_data/case.xlsx
+++ b/data_folder/bev_electronics_wiring/input_data/case.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="71">
   <si>
     <t>Input_FlowID</t>
   </si>
@@ -244,6 +244,12 @@
   </si>
   <si>
     <t>intermediate</t>
+  </si>
+  <si>
+    <t>scenario_alias</t>
+  </si>
+  <si>
+    <t>*=BAU</t>
   </si>
 </sst>
 </file>
@@ -609,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -706,6 +712,14 @@
       </c>
       <c r="B12" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
